--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/02_DealerPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/02_DealerPageTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4F6718-B436-4AE4-90D3-AD659FC4E63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E545BE75-09F9-46F0-93A1-3E0555BC2D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -1637,7 +1637,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1820,6 +1820,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2024,7 +2030,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2038,6 +2044,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2599,7 +2606,7 @@
         <v>56</v>
       </c>
       <c r="F7" s="8"/>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="9" t="s">
         <v>54</v>
       </c>
       <c r="H7" s="1" t="s">
@@ -2678,7 +2685,7 @@
         <v>56</v>
       </c>
       <c r="F10" s="8"/>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="9" t="s">
         <v>54</v>
       </c>
       <c r="H10" s="1" t="s">
@@ -2705,7 +2712,7 @@
         <v>66</v>
       </c>
       <c r="F11" s="8"/>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="9" t="s">
         <v>65</v>
       </c>
       <c r="H11" s="1" t="s">
@@ -2732,7 +2739,7 @@
         <v>69</v>
       </c>
       <c r="F12" s="8"/>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="9" t="s">
         <v>67</v>
       </c>
       <c r="H12" s="1" t="s">
@@ -2809,7 +2816,7 @@
         <v>84</v>
       </c>
       <c r="F15" s="8"/>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="9" t="s">
         <v>54</v>
       </c>
       <c r="H15" s="1" t="s">

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/02_DealerPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/02_DealerPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E545BE75-09F9-46F0-93A1-3E0555BC2D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31AF76C8-AABE-4955-AD7C-5E322D2FDF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -1396,9 +1396,6 @@
 verify_dealerlist_mobileno</t>
   </si>
   <si>
-    <t>Rahul Cement Store</t>
-  </si>
-  <si>
     <t>Dealer Already Mapped</t>
   </si>
   <si>
@@ -1476,6 +1473,9 @@
   </si>
   <si>
     <t>INVOICE_</t>
+  </si>
+  <si>
+    <t>Rahul Kumar</t>
   </si>
 </sst>
 </file>
@@ -2452,7 +2452,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>52</v>
@@ -2466,7 +2466,7 @@
     </row>
     <row r="2" spans="1:9" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>48</v>
@@ -2491,7 +2491,7 @@
     </row>
     <row r="3" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>48</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="4" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>48</v>
@@ -2541,7 +2541,7 @@
     </row>
     <row r="5" spans="1:9" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>48</v>
@@ -2564,7 +2564,7 @@
     </row>
     <row r="6" spans="1:9" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>48</v>
@@ -2591,7 +2591,7 @@
     </row>
     <row r="7" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>48</v>
@@ -2618,7 +2618,7 @@
     </row>
     <row r="8" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>48</v>
@@ -2643,7 +2643,7 @@
     </row>
     <row r="9" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>48</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>48</v>
@@ -2697,7 +2697,7 @@
     </row>
     <row r="11" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>48</v>
@@ -2724,7 +2724,7 @@
     </row>
     <row r="12" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>48</v>
@@ -2736,14 +2736,14 @@
         <v>18</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>5</v>
@@ -2751,7 +2751,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>48</v>
@@ -2763,7 +2763,7 @@
         <v>17</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="14" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>48</v>
@@ -2788,7 +2788,7 @@
         <v>19</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="1"/>
@@ -2801,7 +2801,7 @@
     </row>
     <row r="15" spans="1:9" ht="116" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>48</v>
@@ -2813,7 +2813,7 @@
         <v>20</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="9" t="s">
@@ -2828,7 +2828,7 @@
     </row>
     <row r="16" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>48</v>
@@ -2840,12 +2840,12 @@
         <v>21</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>5</v>
@@ -2853,7 +2853,7 @@
     </row>
     <row r="17" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>48</v>
@@ -2865,14 +2865,14 @@
         <v>23</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>5</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="18" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>48</v>
@@ -2892,12 +2892,12 @@
         <v>42</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>5</v>
@@ -2905,7 +2905,7 @@
     </row>
     <row r="19" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>48</v>
@@ -2917,7 +2917,7 @@
         <v>43</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="1"/>
@@ -2930,7 +2930,7 @@
     </row>
     <row r="20" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>48</v>
@@ -2942,12 +2942,12 @@
         <v>44</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>5</v>
@@ -2955,7 +2955,7 @@
     </row>
     <row r="21" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>48</v>
@@ -2967,12 +2967,12 @@
         <v>22</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>5</v>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/02_DealerPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/02_DealerPageTest.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31AF76C8-AABE-4955-AD7C-5E322D2FDF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486E2F79-B9A3-4AE0-B21A-FB6E0B9790AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="90">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -1476,6 +1477,15 @@
   </si>
   <si>
     <t>Rahul Kumar</t>
+  </si>
+  <si>
+    <t>Kale Treaders</t>
+  </si>
+  <si>
+    <t>Pale Treaders</t>
+  </si>
+  <si>
+    <t>Iale Tbutters</t>
   </si>
 </sst>
 </file>
@@ -2740,7 +2750,7 @@
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>67</v>
@@ -2983,4 +2993,568 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B77D43-4279-44EE-8FFE-039D9F83B8AA}">
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="107" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="56.6328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="57.1796875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.90625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="8"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="8"/>
+      <c r="G7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="8"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="8"/>
+      <c r="G11" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="116" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="8"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="8"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/02_DealerPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/02_DealerPageTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486E2F79-B9A3-4AE0-B21A-FB6E0B9790AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC895627-ED32-4EA8-B315-AC3AF341AB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="90">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -1482,10 +1482,10 @@
     <t>Kale Treaders</t>
   </si>
   <si>
-    <t>Pale Treaders</t>
-  </si>
-  <si>
-    <t>Iale Tbutters</t>
+    <t>EXPECTED_KEY</t>
+  </si>
+  <si>
+    <t>DEALERLIST_DEALERNAME</t>
   </si>
 </sst>
 </file>
@@ -1647,7 +1647,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1836,6 +1836,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2040,7 +2046,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2055,6 +2061,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2431,7 +2442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
@@ -2440,12 +2451,13 @@
     <col min="4" max="4" width="107" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="56.6328125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="56.6328125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="57.1796875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="2"/>
+    <col min="8" max="8" width="56.6328125" style="12" customWidth="1"/>
+    <col min="9" max="9" width="57.1796875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
@@ -2468,13 +2480,16 @@
         <v>52</v>
       </c>
       <c r="H1" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>73</v>
       </c>
@@ -2492,14 +2507,15 @@
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="8"/>
+      <c r="I2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>73</v>
       </c>
@@ -2517,14 +2533,15 @@
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>73</v>
       </c>
@@ -2542,14 +2559,15 @@
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="8"/>
+      <c r="I4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>73</v>
       </c>
@@ -2567,12 +2585,15 @@
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1" t="s">
+      <c r="H5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>73</v>
       </c>
@@ -2592,14 +2613,15 @@
       <c r="G6" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="8"/>
+      <c r="I6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>73</v>
       </c>
@@ -2619,14 +2641,15 @@
       <c r="G7" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="10"/>
+      <c r="I7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>73</v>
       </c>
@@ -2644,14 +2667,15 @@
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="10"/>
+      <c r="I8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>73</v>
       </c>
@@ -2671,14 +2695,15 @@
       <c r="G9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="11"/>
+      <c r="I9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>73</v>
       </c>
@@ -2698,14 +2723,15 @@
       <c r="G10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="10"/>
+      <c r="I10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>73</v>
       </c>
@@ -2725,14 +2751,15 @@
       <c r="G11" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="10"/>
+      <c r="I11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>73</v>
       </c>
@@ -2752,14 +2779,15 @@
       <c r="G12" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="10"/>
+      <c r="I12" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>73</v>
       </c>
@@ -2777,14 +2805,15 @@
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="10"/>
+      <c r="I13" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>73</v>
       </c>
@@ -2802,14 +2831,15 @@
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="10"/>
+      <c r="I14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="116" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="116" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>73</v>
       </c>
@@ -2829,14 +2859,15 @@
       <c r="G15" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="10"/>
+      <c r="I15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>73</v>
       </c>
@@ -2854,14 +2885,15 @@
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="10"/>
+      <c r="I16" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>73</v>
       </c>
@@ -2881,14 +2913,15 @@
         <v>85</v>
       </c>
       <c r="G17" s="1"/>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="10"/>
+      <c r="I17" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>73</v>
       </c>
@@ -2906,14 +2939,15 @@
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="1"/>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="10"/>
+      <c r="I18" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>73</v>
       </c>
@@ -2931,14 +2965,15 @@
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="1"/>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="10"/>
+      <c r="I19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>73</v>
       </c>
@@ -2956,14 +2991,15 @@
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="1"/>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="10"/>
+      <c r="I20" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="J20" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>73</v>
       </c>
@@ -2981,10 +3017,11 @@
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="10"/>
+      <c r="I21" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/02_DealerPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/02_DealerPageTest.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
